--- a/data/trans_orig/LAWTONBRODY_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY_2023-Estudios-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>5,66</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>5,92</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,09; 6,58</t>
+          <t>6,15; 6,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 5,81</t>
+          <t>5,45; 5,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,74; 6,04</t>
+          <t>5,76; 6,06</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>7,39</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,51</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,46</t>
+          <t>7,23</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,52</t>
+          <t>7,21; 7,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,84</t>
+          <t>6,84; 7,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,76</t>
+          <t>7,09; 7,34</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,55</t>
+          <t>7,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,73</t>
+          <t>7,28; 7,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,6</t>
+          <t>7,04; 7,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 7,63</t>
+          <t>7,28; 7,62</t>
         </is>
       </c>
     </row>
@@ -698,17 +698,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>6,96</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6,59</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,56</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,82; 7,09</t>
+          <t>6,87; 7,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,18; 7,29</t>
+          <t>6,08; 6,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 7,15</t>
+          <t>6,46; 6,66</t>
         </is>
       </c>
     </row>
